--- a/유통이력신고 대상품목 기준.xlsx
+++ b/유통이력신고 대상품목 기준.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rbgml\OneDrive\바탕 화면\수입유통신고 자동화파일\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C306871A-7E19-4119-8FEC-06190015929C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5856C663-694D-468B-8855-298E6B14D03A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{6E9385C1-FE1E-4526-A56A-AD4E257C3FB0}"/>
+    <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{6E9385C1-FE1E-4526-A56A-AD4E257C3FB0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>품목</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -69,6 +69,10 @@
   </si>
   <si>
     <t>베트남고추(냉동)</t>
+  </si>
+  <si>
+    <t>신김치(중국산)10kg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -492,15 +496,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BABA3FF0-9EFA-4ABD-ABE7-FB02639A4A43}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="22.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.58203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="26" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" ht="24" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -511,7 +515,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>120450343</v>
       </c>
@@ -522,7 +526,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>120450344</v>
       </c>
@@ -533,7 +537,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>110350814</v>
       </c>
@@ -544,7 +548,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>120751520</v>
       </c>
@@ -555,7 +559,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>250251466</v>
       </c>
@@ -566,7 +570,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>120851542</v>
       </c>
@@ -575,6 +579,17 @@
       </c>
       <c r="C7">
         <v>0.2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>120951580</v>
+      </c>
+      <c r="B8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
